--- a/rulebook-examples/acme-llc/effortless-xlsx/ACME, LLC.xlsx
+++ b/rulebook-examples/acme-llc/effortless-xlsx/ACME, LLC.xlsx
@@ -8,10 +8,12 @@
     <sheet name="Customers" sheetId="1" r:id="rId1"/>
     <sheet name="ERBVersions" sheetId="2" r:id="rId3"/>
     <sheet name="ERBCustomizations" sheetId="3" r:id="rId4"/>
-    <sheet name="_original_json" sheetId="4" r:id="rId5" state="hidden"/>
+    <sheet name="__meta__" sheetId="4" r:id="rId5"/>
+    <sheet name="_original_json" sheetId="5" r:id="rId6" state="hidden"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Customers!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">__meta__!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Customers!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">ERBCustomizations!$A$1:$F$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">ERBVersions!$A$1:$G$1</definedName>
   </definedNames>
@@ -34,7 +36,7 @@
             <color rgb="FFFFFFFF"/>
             <sz val="11"/>
           </rPr>
-          <t>Identifier for the customers.</t>
+          <t>Identifier for the cusfdsfdstomers.</t>
         </r>
       </text>
     </comment>
@@ -51,7 +53,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -64,7 +66,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -94,8 +96,83 @@
 </comments>
 </file>
 
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <d:author xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">CMCC</d:author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Aptos Narrow"/>
+            <b/>
+            <color rgb="FFFFFFFF"/>
+            <sz val="11"/>
+          </rPr>
+          <t>The metadata key (e.g. 'tagline', 'motif_palette', 'substrates'). Unique within the table.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Aptos Narrow"/>
+            <b/>
+            <color rgb="FFFFFFFF"/>
+            <sz val="11"/>
+          </rPr>
+          <t>How to interpret the value columns: 'string' (use StringValue), 'object' (parse JsonValue as JSON object), 'array' (parse JsonValue as JSON array).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Aptos Narrow"/>
+            <b/>
+            <color rgb="FFFFFFFF"/>
+            <sz val="11"/>
+          </rPr>
+          <t>Plain string value. Populated when ValueType == 'string'; null otherwise.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Aptos Narrow"/>
+            <b/>
+            <color rgb="FFFFFFFF"/>
+            <sz val="11"/>
+          </rPr>
+          <t>JSON-encoded value. Populated when ValueType == 'object' or 'array'; null when ValueType == 'string'.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Aptos Narrow"/>
+            <b/>
+            <color rgb="FFFFFFFF"/>
+            <sz val="11"/>
+          </rPr>
+          <t>Identifier for this metadata entry. Mirrors MetaKey so the row is addressable by Name like every other table.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
   <si>
     <t>CustomerId</t>
   </si>
@@ -107,6 +184,9 @@
   </si>
   <si>
     <t>FirstName</t>
+  </si>
+  <si>
+    <t>Initials</t>
   </si>
   <si>
     <t>LastName</t>
@@ -333,12 +413,101 @@
     <t>Data</t>
   </si>
   <si>
+    <t>MetaKey</t>
+  </si>
+  <si>
+    <t>ValueType</t>
+  </si>
+  <si>
+    <t>StringValue</t>
+  </si>
+  <si>
+    <t>JsonValue</t>
+  </si>
+  <si>
+    <t>tagline</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>A one-table customer ledger, filed last-name-first.</t>
+  </si>
+  <si>
+    <t>motif</t>
+  </si>
+  <si>
+    <t>legal-pad</t>
+  </si>
+  <si>
+    <t>motif_palette</t>
+  </si>
+  <si>
+    <t>object</t>
+  </si>
+  <si>
+    <t>{"primary": "#a8941f", "accent": "#4a6741", "ink": "#1f1c0a"}</t>
+  </si>
+  <si>
+    <t>description_rich</t>
+  </si>
+  <si>
+    <t>ACME, LLC is the **leanest possible rulebook with real wiring** — a single business table (`Customers`) and two calculated fields that re-derive themselves from raw inputs. Unlike its larger cousin ACME Corporation, there are no projects, no roles, no approval workflows: just a client ledger where every customer carries *two* identifiers at once. `Name` is a slug minted from the email address; `FullName` is the same person reformatted last-name-first, courtroom-style. Edit one raw field and both derived labels rewrite themselves in every substrate — Postgres view, Python class, Excel cell, OWL ontology — with zero application code.</t>
+  </si>
+  <si>
+    <t>use_cases</t>
+  </si>
+  <si>
+    <t>array</t>
+  </si>
+  <si>
+    <t>["**Rename a customer.** Change `jane-smith-email-com`'s `FirstName` from `Bobby` to `Robert` and watch `FullName` recompute to `Smith, Robert` on the next read — same row, same id, new label.", "**Update an email address.** Edit `john.doe@email.com` to `j.doe@example.com`; the `Name` slug re-derives to `j.doe-example.com` automatically in every substrate.", "**Add a new customer with just the three raw fields** (`EmailAddress`, `FirstName`, `LastName`) and let the rulebook fill in `Name` and `FullName` — no insert triggers, no application logic.", "**Ask the same question of two substrates.** *\"Sort customers alphabetically by surname.\"* The Postgres view and the Python module both return Doe, Jones, Smith — without anyone writing a sort key.", "**Flip the formula in the rulebook** from `LastName &amp; \", \" &amp; FirstName` to `FirstName &amp; \" \" &amp; LastName` and re-run `effortless build`; every substrate now prints western-style names instead of legal-style, with no migration."]</t>
+  </si>
+  <si>
+    <t>signature_rows</t>
+  </si>
+  <si>
+    <t>[{"entity": "Customers", "ids": ["jane-smith-email-com", "john-doe-email-com", "emily-jones-email-com"]}]</t>
+  </si>
+  <si>
+    <t>journal_seed</t>
+  </si>
+  <si>
+    <t>Three customers on file. Each one filed twice — once by email-slug, once by surname-first — and both labels stay in lockstep with the raw fields.</t>
+  </si>
+  <si>
+    <t>substrates</t>
+  </si>
+  <si>
+    <t>[{"key": "postgres", "important": true, "chip_label": "Postgres"}, {"key": "excel", "important": true, "chip_label": "Excel"}, {"key": "python", "important": false, "chip_label": "Python"}, {"key": "owl", "important": false, "chip_label": "OWL"}, {"key": "csv", "important": false, "chip_label": "CSV"}]</t>
+  </si>
+  <si>
+    <t>CMCC_Summary</t>
+  </si>
+  <si>
+    <t>Airtable export with schema-first type mapping: Schemas, Data, Relationships (FK links), Lookups (INDEX/MATCH), Aggregations (SUMIFS/COUNTIFS/Rollups), and Calculated fields (formulas) in Excel dialect. Field types are determined from Airtable's schema metadata FIRST (no coercion); the build FAILS if metadata is unavailable rather than silently inferring from formula/data analysis.</t>
+  </si>
+  <si>
+    <t>conversion_metadata</t>
+  </si>
+  <si>
+    <t>{"source_base_id": "appWrXPvXbkgQGOxt", "table_count": 3, "tool_version": "2.0.0", "field_type_mapping": "checkbox→boolean, number→number/integer, multipleRecordLinks→relationship, multipleLookupValues→lookup, rollup→aggregation, count→aggregation, formula→calculated", "export_mode": "schema_first_type_mapping", "type_inference": {"enabled": true, "priority": "airtable_metadata (NO COERCION) → formula_analysis → reference_resolution → data_analysis (last-resort inference; build SHOULD FAIL rather than silently use this)", "airtable_type_mapping": "checkbox→boolean, singleLineText→string, multilineText→string, number→number/integer, datetime→datetime, singleSelect→string, email→string, url→string, phoneNumber→string", "data_coercion_hierarchy": "Only invoked when Airtable schema is unavailable (which SHOULD make the build fail). Coercion order: datetime → number → integer → boolean → base64 → json → string", "nullable_support": true, "error_value_handling": "#NUM!, #ERROR!, #N/A, #REF!, #DIV/0!, #VALUE!, #NAME? are treated as NULL"}}</t>
+  </si>
+  <si>
     <t xml:space="preserve">{
   "$schema": "https://example.com/cmcc-schema/v1",
   "Name": "ACME, LLC",
-  "Description": "Smallest viable rulebook with a calculated field \u2014 the \"Hello, formulas\" tutorial.",
+  "Description": "Smallest viable rulebook with a calculated field — the \"Hello, formulas\" tutorial.",
   "Customers": {
     "Description": "Table: Customers",
+    "important": true,
+    "summary_rich": "The **client ledger** of ACME, LLC. Every customer is identified two different ways at the same time — a slugified handle derived from their email (`Name`), and a last-name-first legal-style label (`FullName`). Edit either the email or the name parts and both identifiers re-derive themselves the next time any substrate is read.",
+    "important_fields": [
+      "Name",
+      "FullName",
+      "EmailAddress",
+      "LastName"
+    ],
     "schema": [
       {
         "name": "CustomerId",
@@ -351,8 +520,10 @@
         "datatype": "string",
         "type": "calculated",
         "nullable": true,
-        "Description": "Identifier for the customers.",
-        "formula": "=SUBSTITUTE({{EmailAddress}}, \"@\", \"-\")"
+        "Description": "Identifier for the cusfdsfdstomers.",
+        "formula": "=SUBSTITUTE({{EmailAddress}}, \"@\", \"-\")",
+        "important": true,
+        "explanation_rich": "**A handle derived from the email, not the name.** `Name = SUBSTITUTE(EmailAddress, \"@\", \"-\")` — a single character swap turns an address into a slug. Worked example: `jane.smith@email.com` becomes `jane.smith-email.com`, which is what shows up as `Name` in every substrate. Change the customer's email and the handle re-derives itself in Postgres, Python, Excel, and OWL the next read — no application code, no migration."
       },
       {
         "name": "EmailAddress",
@@ -367,6 +538,12 @@
         "type": "raw",
         "nullable": true,
         "Description": "First Name of the customer - used to make the full name"
+      },
+      {
+        "name": "Initials",
+        "datatype": "string",
+        "type": "calculated",
+        "formula": "=LEFT({{FirstName}}, 1) &amp; LEFT({{LastName}}, 1)"
       },
       {
         "name": "LastName",
@@ -381,7 +558,9 @@
         "type": "calculated",
         "nullable": true,
         "Description": "Full name is computed from the first and last name of the customer",
-        "formula": "={{LastName}} &amp; \", \" &amp; {{FirstName}}"
+        "formula": "={{FirstName}} &amp; \" \" &amp; {{LastName}}",
+        "important": true,
+        "explanation_rich": "**Last name first, courtroom-style.** `FullName = LastName &amp; \", \" &amp; FirstName` — the formula is trivial, but the *order* is the point. ACME, LLC files its customers the way a paralegal would: surname, comma, given name. Worked example: `LastName=\"Smith\"` and `FirstName=\"Bobby\"` resolves to `\"Smith, Bobby\"`. Flip the order in the rulebook and every substrate sorts and prints alphabetically by surname on the next read."
       }
     ],
     "data": [
@@ -542,23 +721,119 @@
       }
     ]
   },
-  "_meta": {
-    "_CMCC_Summary": "Airtable export with schema-first type mapping: Schemas, Data, Relationships (FK links), Lookups (INDEX/MATCH), Aggregations (SUMIFS/COUNTIFS/Rollups), and Calculated fields (formulas) in Excel dialect. Field types are determined from Airtable's schema metadata FIRST (no coercion); the build FAILS if metadata is unavailable rather than silently inferring from formula/data analysis.",
-    "_conversion_metadata": {
-      "source_base_id": "appWrXPvXbkgQGOxt",
-      "table_count": 3,
-      "tool_version": "2.0.0",
-      "field_type_mapping": "checkbox\u2192boolean, number\u2192number/integer, multipleRecordLinks\u2192relationship, multipleLookupValues\u2192lookup, rollup\u2192aggregation, count\u2192aggregation, formula\u2192calculated",
-      "export_mode": "schema_first_type_mapping",
-      "type_inference": {
-        "enabled": true,
-        "priority": "airtable_metadata (NO COERCION) \u2192 formula_analysis \u2192 reference_resolution \u2192 data_analysis (last-resort inference; build SHOULD FAIL rather than silently use this)",
-        "airtable_type_mapping": "checkbox\u2192boolean, singleLineText\u2192string, multilineText\u2192string, number\u2192number/integer, datetime\u2192datetime, singleSelect\u2192string, email\u2192string, url\u2192string, phoneNumber\u2192string",
-        "data_coercion_hierarchy": "Only invoked when Airtable schema is unavailable (which SHOULD make the build fail). Coercion order: datetime \u2192 number \u2192 integer \u2192 boolean \u2192 base64 \u2192 json \u2192 string",
-        "nullable_support": true,
-        "error_value_handling": "#NUM!, #ERROR!, #N/A, #REF!, #DIV/0!, #VALUE!, #NAME? are treated as NULL"
+  "__meta__": {
+    "Description": "Project-level metadata that travels with the rulebook: tagline, motif, narrative descriptions, substrate list, signature rows, etc. One row per metadata key. Use ValueType to interpret StringValue vs JsonValue.",
+    "important": false,
+    "schema": [
+      {
+        "name": "MetaKey",
+        "datatype": "string",
+        "type": "raw",
+        "nullable": false,
+        "Description": "The metadata key (e.g. 'tagline', 'motif_palette', 'substrates'). Unique within the table."
+      },
+      {
+        "name": "Name",
+        "datatype": "string",
+        "type": "calculated",
+        "nullable": false,
+        "formula": "={{MetaKey}}",
+        "Description": "Identifier for this metadata entry. Mirrors MetaKey so the row is addressable by Name like every other table."
+      },
+      {
+        "name": "ValueType",
+        "datatype": "string",
+        "type": "raw",
+        "nullable": false,
+        "Description": "How to interpret the value columns: 'string' (use StringValue), 'object' (parse JsonValue as JSON object), 'array' (parse JsonValue as JSON array)."
+      },
+      {
+        "name": "StringValue",
+        "datatype": "string",
+        "type": "raw",
+        "nullable": true,
+        "Description": "Plain string value. Populated when ValueType == 'string'; null otherwise."
+      },
+      {
+        "name": "JsonValue",
+        "datatype": "string",
+        "type": "raw",
+        "nullable": true,
+        "Description": "JSON-encoded value. Populated when ValueType == 'object' or 'array'; null when ValueType == 'string'."
       }
-    }
+    ],
+    "data": [
+      {
+        "MetaKey": "tagline",
+        "Name": "tagline",
+        "ValueType": "string",
+        "StringValue": "A one-table customer ledger, filed last-name-first.",
+        "JsonValue": null
+      },
+      {
+        "MetaKey": "motif",
+        "Name": "motif",
+        "ValueType": "string",
+        "StringValue": "legal-pad",
+        "JsonValue": null
+      },
+      {
+        "MetaKey": "motif_palette",
+        "Name": "motif_palette",
+        "ValueType": "object",
+        "StringValue": null,
+        "JsonValue": "{\"primary\": \"#a8941f\", \"accent\": \"#4a6741\", \"ink\": \"#1f1c0a\"}"
+      },
+      {
+        "MetaKey": "description_rich",
+        "Name": "description_rich",
+        "ValueType": "string",
+        "StringValue": "ACME, LLC is the **leanest possible rulebook with real wiring** — a single business table (`Customers`) and two calculated fields that re-derive themselves from raw inputs. Unlike its larger cousin ACME Corporation, there are no projects, no roles, no approval workflows: just a client ledger where every customer carries *two* identifiers at once. `Name` is a slug minted from the email address; `FullName` is the same person reformatted last-name-first, courtroom-style. Edit one raw field and both derived labels rewrite themselves in every substrate — Postgres view, Python class, Excel cell, OWL ontology — with zero application code.",
+        "JsonValue": null
+      },
+      {
+        "MetaKey": "use_cases",
+        "Name": "use_cases",
+        "ValueType": "array",
+        "StringValue": null,
+        "JsonValue": "[\"**Rename a customer.** Change `jane-smith-email-com`'s `FirstName` from `Bobby` to `Robert` and watch `FullName` recompute to `Smith, Robert` on the next read — same row, same id, new label.\", \"**Update an email address.** Edit `john.doe@email.com` to `j.doe@example.com`; the `Name` slug re-derives to `j.doe-example.com` automatically in every substrate.\", \"**Add a new customer with just the three raw fields** (`EmailAddress`, `FirstName`, `LastName`) and let the rulebook fill in `Name` and `FullName` — no insert triggers, no application logic.\", \"**Ask the same question of two substrates.** *\\\"Sort customers alphabetically by surname.\\\"* The Postgres view and the Python module both return Doe, Jones, Smith — without anyone writing a sort key.\", \"**Flip the formula in the rulebook** from `LastName &amp; \\\", \\\" &amp; FirstName` to `FirstName &amp; \\\" \\\" &amp; LastName` and re-run `effortless build`; every substrate now prints western-style names instead of legal-style, with no migration.\"]"
+      },
+      {
+        "MetaKey": "signature_rows",
+        "Name": "signature_rows",
+        "ValueType": "array",
+        "StringValue": null,
+        "JsonValue": "[{\"entity\": \"Customers\", \"ids\": [\"jane-smith-email-com\", \"john-doe-email-com\", \"emily-jones-email-com\"]}]"
+      },
+      {
+        "MetaKey": "journal_seed",
+        "Name": "journal_seed",
+        "ValueType": "string",
+        "StringValue": "Three customers on file. Each one filed twice — once by email-slug, once by surname-first — and both labels stay in lockstep with the raw fields.",
+        "JsonValue": null
+      },
+      {
+        "MetaKey": "substrates",
+        "Name": "substrates",
+        "ValueType": "array",
+        "StringValue": null,
+        "JsonValue": "[{\"key\": \"postgres\", \"important\": true, \"chip_label\": \"Postgres\"}, {\"key\": \"excel\", \"important\": true, \"chip_label\": \"Excel\"}, {\"key\": \"python\", \"important\": false, \"chip_label\": \"Python\"}, {\"key\": \"owl\", \"important\": false, \"chip_label\": \"OWL\"}, {\"key\": \"csv\", \"important\": false, \"chip_label\": \"CSV\"}]"
+      },
+      {
+        "MetaKey": "CMCC_Summary",
+        "Name": "CMCC_Summary",
+        "ValueType": "string",
+        "StringValue": "Airtable export with schema-first type mapping: Schemas, Data, Relationships (FK links), Lookups (INDEX/MATCH), Aggregations (SUMIFS/COUNTIFS/Rollups), and Calculated fields (formulas) in Excel dialect. Field types are determined from Airtable's schema metadata FIRST (no coercion); the build FAILS if metadata is unavailable rather than silently inferring from formula/data analysis.",
+        "JsonValue": null
+      },
+      {
+        "MetaKey": "conversion_metadata",
+        "Name": "conversion_metadata",
+        "ValueType": "object",
+        "StringValue": null,
+        "JsonValue": "{\"source_base_id\": \"appWrXPvXbkgQGOxt\", \"table_count\": 3, \"tool_version\": \"2.0.0\", \"field_type_mapping\": \"checkbox→boolean, number→number/integer, multipleRecordLinks→relationship, multipleLookupValues→lookup, rollup→aggregation, count→aggregation, formula→calculated\", \"export_mode\": \"schema_first_type_mapping\", \"type_inference\": {\"enabled\": true, \"priority\": \"airtable_metadata (NO COERCION) → formula_analysis → reference_resolution → data_analysis (last-resort inference; build SHOULD FAIL rather than silently use this)\", \"airtable_type_mapping\": \"checkbox→boolean, singleLineText→string, multilineText→string, number→number/integer, datetime→datetime, singleSelect→string, email→string, url→string, phoneNumber→string\", \"data_coercion_hierarchy\": \"Only invoked when Airtable schema is unavailable (which SHOULD make the build fail). Coercion order: datetime → number → integer → boolean → base64 → json → string\", \"nullable_support\": true, \"error_value_handling\": \"#NUM!, #ERROR!, #N/A, #REF!, #DIV/0!, #VALUE!, #NAME? are treated as NULL\"}}"
+      }
+    ]
   }
 }
 </t>
@@ -631,7 +906,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.053359985351562" customWidth="1"/>
@@ -640,6 +915,7 @@
     <col min="4" max="4" width="17.443378448486328" customWidth="1"/>
     <col min="5" max="5" width="17.443378448486328" customWidth="1"/>
     <col min="6" max="6" width="17.443378448486328" customWidth="1"/>
+    <col min="7" max="7" width="17.443378448486328" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -661,75 +937,90 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="3" t="str">
         <f>SUBSTITUTE(C2, "@", "-")</f>
         <v>jane.smith-email.com</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="3" t="str">
-        <f>E2 &amp; ", " &amp; D2</f>
-        <v>Smith, Bobby</v>
+      <c r="E2" s="3" t="str">
+        <f>LEFT(D2, 1) &amp; LEFT(F2, 1)</f>
+        <v>BS</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="3" t="str">
+        <f>D2 &amp; " " &amp; F2</f>
+        <v>Bobby Smith</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="3" t="str">
         <f>SUBSTITUTE(C3, "@", "-")</f>
         <v>john.doe-email.com</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="3" t="str">
-        <f>E3 &amp; ", " &amp; D3</f>
-        <v>Doe, Jimmy</v>
+      <c r="E3" s="3" t="str">
+        <f>LEFT(D3, 1) &amp; LEFT(F3, 1)</f>
+        <v>JD</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="3" t="str">
+        <f>D3 &amp; " " &amp; F3</f>
+        <v>Jimmy Doe</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" s="3" t="str">
         <f>SUBSTITUTE(C4, "@", "-")</f>
         <v>emily.jones-email.com</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="3" t="str">
-        <f>E4 &amp; ", " &amp; D4</f>
-        <v>Jones, Mary</v>
+      <c r="E4" s="3" t="str">
+        <f>LEFT(D4, 1) &amp; LEFT(F4, 1)</f>
+        <v>MJ</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="3" t="str">
+        <f>D4 &amp; " " &amp; F4</f>
+        <v>Mary Jones</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:G1"/>
   <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -751,25 +1042,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -793,122 +1084,122 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -919,12 +1210,201 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" s="3" t="str">
+        <f>A2</f>
+        <v>tagline</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="3" t="str">
+        <f>A3</f>
+        <v>motif</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" s="3" t="str">
+        <f>A4</f>
+        <v>motif_palette</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" s="3" t="str">
+        <f>A5</f>
+        <v>description_rich</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="3" t="str">
+        <f>A6</f>
+        <v>use_cases</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="3" t="str">
+        <f>A7</f>
+        <v>signature_rows</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="3" t="str">
+        <f>A8</f>
+        <v>journal_seed</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="3" t="str">
+        <f>A9</f>
+        <v>substrates</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="3" t="str">
+        <f>A10</f>
+        <v>CMCC_Summary</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="3" t="str">
+        <f>A11</f>
+        <v>conversion_metadata</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/rulebook-examples/acme-llc/effortless-xlsx/ACME, LLC.xlsx
+++ b/rulebook-examples/acme-llc/effortless-xlsx/ACME, LLC.xlsx
@@ -172,7 +172,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t>CustomerId</t>
   </si>
@@ -494,6 +494,12 @@
     <t>{"source_base_id": "appWrXPvXbkgQGOxt", "table_count": 3, "tool_version": "2.0.0", "field_type_mapping": "checkbox→boolean, number→number/integer, multipleRecordLinks→relationship, multipleLookupValues→lookup, rollup→aggregation, count→aggregation, formula→calculated", "export_mode": "schema_first_type_mapping", "type_inference": {"enabled": true, "priority": "airtable_metadata (NO COERCION) → formula_analysis → reference_resolution → data_analysis (last-resort inference; build SHOULD FAIL rather than silently use this)", "airtable_type_mapping": "checkbox→boolean, singleLineText→string, multilineText→string, number→number/integer, datetime→datetime, singleSelect→string, email→string, url→string, phoneNumber→string", "data_coercion_hierarchy": "Only invoked when Airtable schema is unavailable (which SHOULD make the build fail). Coercion order: datetime → number → integer → boolean → base64 → json → string", "nullable_support": true, "error_value_handling": "#NUM!, #ERROR!, #N/A, #REF!, #DIV/0!, #VALUE!, #NAME? are treated as NULL"}}</t>
   </si>
   <si>
+    <t>narrative_drift_lesson</t>
+  </si>
+  <si>
+    <t>**The point of this demo is the asymmetry between code and prose.** Flip `FullName` from `LastName &amp; ", " &amp; FirstName` (legal-style, surname-first) to `FirstName &amp; " " &amp; LastName` (western order) and re-run `effortless build`: every *executable* artifact follows along instantly and for free — the Postgres view, Python class, Go SDK, Excel/CSV, OWL, the rendered RuleSpeak DRs and section-4 expression all re-derive from the single formula and stay correct. But every *hand-written* narrative about the rules goes stale from one moment to the next — `description_rich`, `explanation_rich`, `journal_seed`, the seed `FullName` values baked into the Customers rows, and any prose README still say "Smith, Bobby / courtroom-style" even though the formula now computes "Bobby Smith". That staleness is INTENTIONAL and left in place on purpose: it is the live exhibit. Computed code follows the SSoT; comments and narrative cannot. The only narrative that can keep up is one that is itself regenerated from the rulebook (e.g. an LLM-generated README), not hand-maintained. Do not "fix" the stale narrative or seed values to match the formula — doing so erases the demonstration.</t>
+  </si>
+  <si>
     <t xml:space="preserve">{
   "$schema": "https://example.com/cmcc-schema/v1",
   "Name": "ACME, LLC",
@@ -832,6 +838,13 @@
         "ValueType": "object",
         "StringValue": null,
         "JsonValue": "{\"source_base_id\": \"appWrXPvXbkgQGOxt\", \"table_count\": 3, \"tool_version\": \"2.0.0\", \"field_type_mapping\": \"checkbox→boolean, number→number/integer, multipleRecordLinks→relationship, multipleLookupValues→lookup, rollup→aggregation, count→aggregation, formula→calculated\", \"export_mode\": \"schema_first_type_mapping\", \"type_inference\": {\"enabled\": true, \"priority\": \"airtable_metadata (NO COERCION) → formula_analysis → reference_resolution → data_analysis (last-resort inference; build SHOULD FAIL rather than silently use this)\", \"airtable_type_mapping\": \"checkbox→boolean, singleLineText→string, multilineText→string, number→number/integer, datetime→datetime, singleSelect→string, email→string, url→string, phoneNumber→string\", \"data_coercion_hierarchy\": \"Only invoked when Airtable schema is unavailable (which SHOULD make the build fail). Coercion order: datetime → number → integer → boolean → base64 → json → string\", \"nullable_support\": true, \"error_value_handling\": \"#NUM!, #ERROR!, #N/A, #REF!, #DIV/0!, #VALUE!, #NAME? are treated as NULL\"}}"
+      },
+      {
+        "MetaKey": "narrative_drift_lesson",
+        "Name": "narrative_drift_lesson",
+        "ValueType": "string",
+        "StringValue": "**The point of this demo is the asymmetry between code and prose.** Flip `FullName` from `LastName &amp; \", \" &amp; FirstName` (legal-style, surname-first) to `FirstName &amp; \" \" &amp; LastName` (western order) and re-run `effortless build`: every *executable* artifact follows along instantly and for free — the Postgres view, Python class, Go SDK, Excel/CSV, OWL, the rendered RuleSpeak DRs and section-4 expression all re-derive from the single formula and stay correct. But every *hand-written* narrative about the rules goes stale from one moment to the next — `description_rich`, `explanation_rich`, `journal_seed`, the seed `FullName` values baked into the Customers rows, and any prose README still say \"Smith, Bobby / courtroom-style\" even though the formula now computes \"Bobby Smith\". That staleness is INTENTIONAL and left in place on purpose: it is the live exhibit. Computed code follows the SSoT; comments and narrative cannot. The only narrative that can keep up is one that is itself regenerated from the rulebook (e.g. an LLM-generated README), not hand-maintained. Do not \"fix\" the stale narrative or seed values to match the formula — doing so erases the demonstration.",
+        "JsonValue": null
       }
     ]
   }
@@ -1210,7 +1223,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1389,6 +1402,22 @@
       <c r="E11" s="2" t="s">
         <v>82</v>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" s="3" t="str">
+        <f>A12</f>
+        <v>narrative_drift_lesson</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>
@@ -1404,7 +1433,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
